--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -98,6 +98,51 @@
   </si>
   <si>
     <t xml:space="preserve">사거리와 관통력이 뛰어난 최강의 포</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_Canon_0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 1 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_Canon_0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 2 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_Canon_0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 3 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_Canon_0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 4 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_Canon_0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접공격 5 이다</t>
   </si>
 </sst>
 </file>
@@ -695,10 +740,18 @@
       <c r="O9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -712,10 +765,18 @@
       <c r="O10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -729,10 +790,18 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -746,10 +815,18 @@
       <c r="O12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>80</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -763,10 +840,18 @@
       <c r="O13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -20,18 +20,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
   <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 쿨다운</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격범위</t>
+  </si>
+  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
+    <t xml:space="preserve">float</t>
   </si>
   <si>
     <t xml:space="preserve">Id</t>
@@ -44,6 +56,12 @@
   </si>
   <si>
     <t xml:space="preserve">Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireCoolDown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireRange </t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_Canon_0001</t>
@@ -549,61 +567,88 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="46.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -616,19 +661,23 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -641,19 +690,23 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -666,19 +719,23 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -691,19 +748,23 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -716,19 +777,23 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -741,19 +806,23 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -766,19 +835,23 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -791,19 +864,23 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -816,19 +893,23 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -841,19 +922,23 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -869,7 +954,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -886,125 +971,140 @@
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="5"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="5"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="5"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">공격범위</t>
   </si>
   <si>
+    <t xml:space="preserve">공격프리팹 경로</t>
+  </si>
+  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t xml:space="preserve">FireRange </t>
   </si>
   <si>
+    <t xml:space="preserve">AttackPrefab</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0001</t>
   </si>
   <si>
@@ -73,6 +79,28 @@
     <t xml:space="preserve">기초적인 대포</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Prefabs/Attack/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">CanonBall</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0002</t>
   </si>
   <si>
@@ -125,6 +153,28 @@
   </si>
   <si>
     <t xml:space="preserve">근접공격 1 이다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Prefabs/Attack/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">CloseAttack</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Weapon_Canon_0008</t>
@@ -170,7 +220,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -208,6 +258,19 @@
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF000000"/>
+      <name val="DotumChe"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
       <charset val="129"/>
     </font>
     <font>
@@ -279,7 +342,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -296,7 +359,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -304,7 +375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,7 +633,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.1"/>
@@ -570,6 +641,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -586,525 +658,569 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="G9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="G10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="F11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="G11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="D14" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -37,6 +37,12 @@
     <t xml:space="preserve">공격범위</t>
   </si>
   <si>
+    <t xml:space="preserve">가격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아이콘</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격프리팹 경로</t>
   </si>
   <si>
@@ -49,6 +55,9 @@
     <t xml:space="preserve">float</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -67,6 +76,12 @@
     <t xml:space="preserve">FireRange </t>
   </si>
   <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconPath</t>
+  </si>
+  <si>
     <t xml:space="preserve">AttackPrefab</t>
   </si>
   <si>
@@ -77,6 +92,9 @@
   </si>
   <si>
     <t xml:space="preserve">기초적인 대포</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0001</t>
   </si>
   <si>
     <r>
@@ -110,6 +128,9 @@
     <t xml:space="preserve">표준적인 대포</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0003</t>
   </si>
   <si>
@@ -119,6 +140,9 @@
     <t xml:space="preserve">위력이 상승한 포</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0004</t>
   </si>
   <si>
@@ -128,6 +152,9 @@
     <t xml:space="preserve">중장거리에서 강력한 포</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0005</t>
   </si>
   <si>
@@ -137,6 +164,9 @@
     <t xml:space="preserve">최고의 관통력을 자랑하는 포</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0005</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0006</t>
   </si>
   <si>
@@ -146,6 +176,9 @@
     <t xml:space="preserve">사거리와 관통력이 뛰어난 최강의 포</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0007</t>
   </si>
   <si>
@@ -153,6 +186,9 @@
   </si>
   <si>
     <t xml:space="preserve">근접공격 1 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0007</t>
   </si>
   <si>
     <r>
@@ -186,6 +222,9 @@
     <t xml:space="preserve">근접공격 2 이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0008</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0009</t>
   </si>
   <si>
@@ -195,6 +234,9 @@
     <t xml:space="preserve">근접공격 3 이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0009</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0010</t>
   </si>
   <si>
@@ -204,6 +246,9 @@
     <t xml:space="preserve">근접공격 4 이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0010</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_Canon_0011</t>
   </si>
   <si>
@@ -211,6 +256,9 @@
   </si>
   <si>
     <t xml:space="preserve">근접공격 5 이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon/Weapon/weapon_0011</t>
   </si>
 </sst>
 </file>
@@ -220,7 +268,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -254,6 +302,13 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
@@ -261,17 +316,18 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="9.5"/>
       <color rgb="FF000000"/>
       <name val="DotumChe"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -342,7 +398,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -355,15 +411,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -375,7 +443,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -633,7 +701,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P1000"/>
+  <dimension ref="A1:R1000"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.1"/>
@@ -641,7 +709,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="22.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -664,563 +732,649 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="G7" s="9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="G8" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="G9" s="9" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="G10" s="9" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="G11" s="9" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="F12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G13" s="9" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="G14" s="9" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
